--- a/Option-Scanner/Dashboard/OI_Volume_Alerts.xlsx
+++ b/Option-Scanner/Dashboard/OI_Volume_Alerts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2224"/>
+  <dimension ref="A1:K2330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73458,8 +73458,6 @@
       <c r="G2224" t="n">
         <v>-528645</v>
       </c>
-      <c r="H2224" t="inlineStr"/>
-      <c r="I2224" t="inlineStr"/>
       <c r="J2224" t="inlineStr">
         <is>
           <t>BELOW</t>
@@ -73468,6 +73466,3558 @@
       <c r="K2224" t="inlineStr">
         <is>
           <t>OI poll change +6.7% vs last scan (OI chg -528,645 | oi=7,356,505, was=7,885,150)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2225">
+      <c r="A2225" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:18:53</t>
+        </is>
+      </c>
+      <c r="B2225" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2225" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23300 CALL</t>
+        </is>
+      </c>
+      <c r="D2225" t="n">
+        <v>4273425</v>
+      </c>
+      <c r="E2225" t="n">
+        <v>3143205</v>
+      </c>
+      <c r="F2225" t="n">
+        <v>36</v>
+      </c>
+      <c r="G2225" t="n">
+        <v>1130220</v>
+      </c>
+      <c r="H2225" t="n">
+        <v>3401255</v>
+      </c>
+      <c r="K2225" t="inlineStr">
+        <is>
+          <t>periodic record vol=3,401,255 oi=4,273,425 (OI chg +1,130,220 +36.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2226">
+      <c r="A2226" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:18:55</t>
+        </is>
+      </c>
+      <c r="B2226" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2226" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23250 CALL</t>
+        </is>
+      </c>
+      <c r="D2226" t="n">
+        <v>302315</v>
+      </c>
+      <c r="E2226" t="n">
+        <v>126360</v>
+      </c>
+      <c r="F2226" t="n">
+        <v>139.2</v>
+      </c>
+      <c r="G2226" t="n">
+        <v>175955</v>
+      </c>
+      <c r="H2226" t="n">
+        <v>483340</v>
+      </c>
+      <c r="K2226" t="inlineStr">
+        <is>
+          <t>periodic record vol=483,340 oi=302,315 (OI chg +175,955 +139.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2227">
+      <c r="A2227" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:18:56</t>
+        </is>
+      </c>
+      <c r="B2227" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2227" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23200 CALL</t>
+        </is>
+      </c>
+      <c r="D2227" t="n">
+        <v>715715</v>
+      </c>
+      <c r="E2227" t="n">
+        <v>464880</v>
+      </c>
+      <c r="F2227" t="n">
+        <v>54</v>
+      </c>
+      <c r="G2227" t="n">
+        <v>250835</v>
+      </c>
+      <c r="H2227" t="n">
+        <v>699595</v>
+      </c>
+      <c r="K2227" t="inlineStr">
+        <is>
+          <t>periodic record vol=699,595 oi=715,715 (OI chg +250,835 +54.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2228">
+      <c r="A2228" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:18:56</t>
+        </is>
+      </c>
+      <c r="B2228" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2228" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23300 PUT</t>
+        </is>
+      </c>
+      <c r="D2228" t="n">
+        <v>5594485</v>
+      </c>
+      <c r="E2228" t="n">
+        <v>5011045</v>
+      </c>
+      <c r="F2228" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G2228" t="n">
+        <v>583440</v>
+      </c>
+      <c r="H2228" t="n">
+        <v>7151365</v>
+      </c>
+      <c r="K2228" t="inlineStr">
+        <is>
+          <t>periodic record vol=7,151,365 oi=5,594,485 (OI chg +583,440 +11.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2229">
+      <c r="A2229" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:18:57</t>
+        </is>
+      </c>
+      <c r="B2229" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2229" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23350 PUT</t>
+        </is>
+      </c>
+      <c r="D2229" t="n">
+        <v>1239355</v>
+      </c>
+      <c r="E2229" t="n">
+        <v>816270</v>
+      </c>
+      <c r="F2229" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="G2229" t="n">
+        <v>423085</v>
+      </c>
+      <c r="H2229" t="n">
+        <v>4143295</v>
+      </c>
+      <c r="K2229" t="inlineStr">
+        <is>
+          <t>periodic record vol=4,143,295 oi=1,239,355 (OI chg +423,085 +51.8%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2230">
+      <c r="A2230" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:18:58</t>
+        </is>
+      </c>
+      <c r="B2230" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2230" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23400 PUT</t>
+        </is>
+      </c>
+      <c r="D2230" t="n">
+        <v>3586635</v>
+      </c>
+      <c r="E2230" t="n">
+        <v>2959840</v>
+      </c>
+      <c r="F2230" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="G2230" t="n">
+        <v>626795</v>
+      </c>
+      <c r="H2230" t="n">
+        <v>6773975</v>
+      </c>
+      <c r="K2230" t="inlineStr">
+        <is>
+          <t>periodic record vol=6,773,975 oi=3,586,635 (OI chg +626,795 +21.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2231">
+      <c r="A2231" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:19:12</t>
+        </is>
+      </c>
+      <c r="B2231" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2231" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23300 CALL</t>
+        </is>
+      </c>
+      <c r="D2231" t="n">
+        <v>4643665</v>
+      </c>
+      <c r="E2231" t="n">
+        <v>4273425</v>
+      </c>
+      <c r="F2231" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="G2231" t="n">
+        <v>370240</v>
+      </c>
+      <c r="J2231" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2231" t="inlineStr">
+        <is>
+          <t>OI poll change +8.7% vs last scan (OI chg +370,240 | oi=4,643,665, was=4,273,425)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2232">
+      <c r="A2232" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:19:13</t>
+        </is>
+      </c>
+      <c r="B2232" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2232" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23250 CALL</t>
+        </is>
+      </c>
+      <c r="D2232" t="n">
+        <v>342745</v>
+      </c>
+      <c r="E2232" t="n">
+        <v>302315</v>
+      </c>
+      <c r="F2232" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="G2232" t="n">
+        <v>40430</v>
+      </c>
+      <c r="J2232" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2232" t="inlineStr">
+        <is>
+          <t>OI poll change +13.4% vs last scan (OI chg +40,430 | oi=342,745, was=302,315)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2233">
+      <c r="A2233" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:19:14</t>
+        </is>
+      </c>
+      <c r="B2233" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2233" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23200 CALL</t>
+        </is>
+      </c>
+      <c r="D2233" t="n">
+        <v>772850</v>
+      </c>
+      <c r="E2233" t="n">
+        <v>715715</v>
+      </c>
+      <c r="F2233" t="n">
+        <v>8</v>
+      </c>
+      <c r="G2233" t="n">
+        <v>57135</v>
+      </c>
+      <c r="J2233" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2233" t="inlineStr">
+        <is>
+          <t>OI poll change +8.0% vs last scan (OI chg +57,135 | oi=772,850, was=715,715)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2234">
+      <c r="A2234" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:19:15</t>
+        </is>
+      </c>
+      <c r="B2234" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2234" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23350 PUT</t>
+        </is>
+      </c>
+      <c r="D2234" t="n">
+        <v>1313000</v>
+      </c>
+      <c r="E2234" t="n">
+        <v>1239355</v>
+      </c>
+      <c r="F2234" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G2234" t="n">
+        <v>73645</v>
+      </c>
+      <c r="J2234" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2234" t="inlineStr">
+        <is>
+          <t>OI poll change +5.9% vs last scan (OI chg +73,645 | oi=1,313,000, was=1,239,355)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2235">
+      <c r="A2235" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:20:02</t>
+        </is>
+      </c>
+      <c r="B2235" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2235" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="K2235" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: +1,072,760 | New PE Vol: +4,267,380</t>
+        </is>
+      </c>
+    </row>
+    <row r="2236">
+      <c r="A2236" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:21:07</t>
+        </is>
+      </c>
+      <c r="B2236" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2236" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="K2236" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: +1,756,170 | New PE Vol: +3,801,655</t>
+        </is>
+      </c>
+    </row>
+    <row r="2237">
+      <c r="A2237" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:21:15</t>
+        </is>
+      </c>
+      <c r="B2237" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2237" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23300 CALL</t>
+        </is>
+      </c>
+      <c r="D2237" t="n">
+        <v>5466305</v>
+      </c>
+      <c r="E2237" t="n">
+        <v>5021965</v>
+      </c>
+      <c r="F2237" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G2237" t="n">
+        <v>444340</v>
+      </c>
+      <c r="J2237" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2237" t="inlineStr">
+        <is>
+          <t>OI poll change +8.8% vs last scan (OI chg +444,340 | oi=5,466,305, was=5,021,965)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2238">
+      <c r="A2238" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:21:16</t>
+        </is>
+      </c>
+      <c r="B2238" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2238" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23250 CALL</t>
+        </is>
+      </c>
+      <c r="D2238" t="n">
+        <v>503295</v>
+      </c>
+      <c r="E2238" t="n">
+        <v>411450</v>
+      </c>
+      <c r="F2238" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G2238" t="n">
+        <v>91845</v>
+      </c>
+      <c r="J2238" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2238" t="inlineStr">
+        <is>
+          <t>OI poll change +22.3% vs last scan (OI chg +91,845 | oi=503,295, was=411,450)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2239">
+      <c r="A2239" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:21:17</t>
+        </is>
+      </c>
+      <c r="B2239" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2239" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23200 CALL</t>
+        </is>
+      </c>
+      <c r="D2239" t="n">
+        <v>930410</v>
+      </c>
+      <c r="E2239" t="n">
+        <v>857285</v>
+      </c>
+      <c r="F2239" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G2239" t="n">
+        <v>73125</v>
+      </c>
+      <c r="J2239" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2239" t="inlineStr">
+        <is>
+          <t>OI poll change +8.5% vs last scan (OI chg +73,125 | oi=930,410, was=857,285)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2240">
+      <c r="A2240" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:26:03</t>
+        </is>
+      </c>
+      <c r="B2240" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2240" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23300 CALL</t>
+        </is>
+      </c>
+      <c r="D2240" t="n">
+        <v>6396910</v>
+      </c>
+      <c r="E2240" t="n">
+        <v>5466305</v>
+      </c>
+      <c r="F2240" t="n">
+        <v>17</v>
+      </c>
+      <c r="G2240" t="n">
+        <v>930605</v>
+      </c>
+      <c r="J2240" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2240" t="inlineStr">
+        <is>
+          <t>OI poll change +17.0% vs last scan (OI chg +930,605 | oi=6,396,910, was=5,466,305)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2241">
+      <c r="A2241" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:26:04</t>
+        </is>
+      </c>
+      <c r="B2241" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2241" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23250 CALL</t>
+        </is>
+      </c>
+      <c r="D2241" t="n">
+        <v>661310</v>
+      </c>
+      <c r="E2241" t="n">
+        <v>503295</v>
+      </c>
+      <c r="F2241" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="G2241" t="n">
+        <v>158015</v>
+      </c>
+      <c r="J2241" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2241" t="inlineStr">
+        <is>
+          <t>OI poll change +31.4% vs last scan (OI chg +158,015 | oi=661,310, was=503,295)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2242">
+      <c r="A2242" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:26:05</t>
+        </is>
+      </c>
+      <c r="B2242" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2242" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23200 CALL</t>
+        </is>
+      </c>
+      <c r="D2242" t="n">
+        <v>1073605</v>
+      </c>
+      <c r="E2242" t="n">
+        <v>930410</v>
+      </c>
+      <c r="F2242" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="G2242" t="n">
+        <v>143195</v>
+      </c>
+      <c r="J2242" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2242" t="inlineStr">
+        <is>
+          <t>OI poll change +15.4% vs last scan (OI chg +143,195 | oi=1,073,605, was=930,410)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2243">
+      <c r="A2243" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:26:06</t>
+        </is>
+      </c>
+      <c r="B2243" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2243" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23350 PUT</t>
+        </is>
+      </c>
+      <c r="D2243" t="n">
+        <v>1559350</v>
+      </c>
+      <c r="E2243" t="n">
+        <v>1325610</v>
+      </c>
+      <c r="F2243" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G2243" t="n">
+        <v>233740</v>
+      </c>
+      <c r="J2243" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2243" t="inlineStr">
+        <is>
+          <t>OI poll change +17.6% vs last scan (OI chg +233,740 | oi=1,559,350, was=1,325,610)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2244">
+      <c r="A2244" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:26:07</t>
+        </is>
+      </c>
+      <c r="B2244" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2244" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23400 PUT</t>
+        </is>
+      </c>
+      <c r="D2244" t="n">
+        <v>3797430</v>
+      </c>
+      <c r="E2244" t="n">
+        <v>3593915</v>
+      </c>
+      <c r="F2244" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="G2244" t="n">
+        <v>203515</v>
+      </c>
+      <c r="J2244" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2244" t="inlineStr">
+        <is>
+          <t>OI poll change +5.7% vs last scan (OI chg +203,515 | oi=3,797,430, was=3,593,915)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2245">
+      <c r="A2245" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:26:07</t>
+        </is>
+      </c>
+      <c r="B2245" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2245" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23300 CALL</t>
+        </is>
+      </c>
+      <c r="D2245" t="n">
+        <v>6396910</v>
+      </c>
+      <c r="E2245" t="n">
+        <v>3143205</v>
+      </c>
+      <c r="F2245" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="G2245" t="n">
+        <v>3253705</v>
+      </c>
+      <c r="H2245" t="n">
+        <v>8891740</v>
+      </c>
+      <c r="K2245" t="inlineStr">
+        <is>
+          <t>periodic record vol=8,891,740 oi=6,396,910 (OI chg +3,253,705 +103.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2246">
+      <c r="A2246" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:26:09</t>
+        </is>
+      </c>
+      <c r="B2246" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2246" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23250 CALL</t>
+        </is>
+      </c>
+      <c r="D2246" t="n">
+        <v>661310</v>
+      </c>
+      <c r="E2246" t="n">
+        <v>126360</v>
+      </c>
+      <c r="F2246" t="n">
+        <v>423.4</v>
+      </c>
+      <c r="G2246" t="n">
+        <v>534950</v>
+      </c>
+      <c r="H2246" t="n">
+        <v>1416610</v>
+      </c>
+      <c r="K2246" t="inlineStr">
+        <is>
+          <t>periodic record vol=1,416,610 oi=661,310 (OI chg +534,950 +423.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2247">
+      <c r="A2247" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:26:10</t>
+        </is>
+      </c>
+      <c r="B2247" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2247" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23200 CALL</t>
+        </is>
+      </c>
+      <c r="D2247" t="n">
+        <v>1073605</v>
+      </c>
+      <c r="E2247" t="n">
+        <v>464880</v>
+      </c>
+      <c r="F2247" t="n">
+        <v>130.9</v>
+      </c>
+      <c r="G2247" t="n">
+        <v>608725</v>
+      </c>
+      <c r="H2247" t="n">
+        <v>1645150</v>
+      </c>
+      <c r="K2247" t="inlineStr">
+        <is>
+          <t>periodic record vol=1,645,150 oi=1,073,605 (OI chg +608,725 +130.9%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2248">
+      <c r="A2248" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:26:11</t>
+        </is>
+      </c>
+      <c r="B2248" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2248" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23300 PUT</t>
+        </is>
+      </c>
+      <c r="D2248" t="n">
+        <v>6366555</v>
+      </c>
+      <c r="E2248" t="n">
+        <v>5011045</v>
+      </c>
+      <c r="F2248" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="G2248" t="n">
+        <v>1355510</v>
+      </c>
+      <c r="H2248" t="n">
+        <v>17602130</v>
+      </c>
+      <c r="K2248" t="inlineStr">
+        <is>
+          <t>periodic record vol=17,602,130 oi=6,366,555 (OI chg +1,355,510 +27.1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2249">
+      <c r="A2249" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:26:12</t>
+        </is>
+      </c>
+      <c r="B2249" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2249" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23350 PUT</t>
+        </is>
+      </c>
+      <c r="D2249" t="n">
+        <v>1559350</v>
+      </c>
+      <c r="E2249" t="n">
+        <v>816270</v>
+      </c>
+      <c r="F2249" t="n">
+        <v>91</v>
+      </c>
+      <c r="G2249" t="n">
+        <v>743080</v>
+      </c>
+      <c r="H2249" t="n">
+        <v>7491900</v>
+      </c>
+      <c r="K2249" t="inlineStr">
+        <is>
+          <t>periodic record vol=7,491,900 oi=1,559,350 (OI chg +743,080 +91.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2250">
+      <c r="A2250" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:26:13</t>
+        </is>
+      </c>
+      <c r="B2250" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2250" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23400 PUT</t>
+        </is>
+      </c>
+      <c r="D2250" t="n">
+        <v>3797430</v>
+      </c>
+      <c r="E2250" t="n">
+        <v>2959840</v>
+      </c>
+      <c r="F2250" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="G2250" t="n">
+        <v>837590</v>
+      </c>
+      <c r="H2250" t="n">
+        <v>10467145</v>
+      </c>
+      <c r="K2250" t="inlineStr">
+        <is>
+          <t>periodic record vol=10,467,145 oi=3,797,430 (OI chg +837,590 +28.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2251">
+      <c r="A2251" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:26:14</t>
+        </is>
+      </c>
+      <c r="B2251" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2251" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="K2251" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: +4,540,380 | New PE Vol: +9,423,505</t>
+        </is>
+      </c>
+    </row>
+    <row r="2252">
+      <c r="A2252" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:27:15</t>
+        </is>
+      </c>
+      <c r="B2252" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2252" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="K2252" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: +1,292,460 | New PE Vol: +2,981,290</t>
+        </is>
+      </c>
+    </row>
+    <row r="2253">
+      <c r="A2253" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:28:18</t>
+        </is>
+      </c>
+      <c r="B2253" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2253" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23250 CALL</t>
+        </is>
+      </c>
+      <c r="D2253" t="n">
+        <v>817570</v>
+      </c>
+      <c r="E2253" t="n">
+        <v>733330</v>
+      </c>
+      <c r="F2253" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G2253" t="n">
+        <v>84240</v>
+      </c>
+      <c r="J2253" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2253" t="inlineStr">
+        <is>
+          <t>OI poll change +11.5% vs last scan (OI chg +84,240 | oi=817,570, was=733,330)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2254">
+      <c r="A2254" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:28:19</t>
+        </is>
+      </c>
+      <c r="B2254" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2254" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23200 CALL</t>
+        </is>
+      </c>
+      <c r="D2254" t="n">
+        <v>1212315</v>
+      </c>
+      <c r="E2254" t="n">
+        <v>1125865</v>
+      </c>
+      <c r="F2254" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="G2254" t="n">
+        <v>86450</v>
+      </c>
+      <c r="J2254" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2254" t="inlineStr">
+        <is>
+          <t>OI poll change +7.7% vs last scan (OI chg +86,450 | oi=1,212,315, was=1,125,865)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2255">
+      <c r="A2255" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:28:20</t>
+        </is>
+      </c>
+      <c r="B2255" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2255" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23150 CALL</t>
+        </is>
+      </c>
+      <c r="D2255" t="n">
+        <v>202280</v>
+      </c>
+      <c r="E2255" t="n">
+        <v>172640</v>
+      </c>
+      <c r="F2255" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="G2255" t="n">
+        <v>29640</v>
+      </c>
+      <c r="J2255" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2255" t="inlineStr">
+        <is>
+          <t>OI poll change +17.2% vs last scan (OI chg +29,640 | oi=202,280, was=172,640)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2256">
+      <c r="A2256" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:28:21</t>
+        </is>
+      </c>
+      <c r="B2256" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2256" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23250 PUT</t>
+        </is>
+      </c>
+      <c r="D2256" t="n">
+        <v>1739790</v>
+      </c>
+      <c r="E2256" t="n">
+        <v>1637090</v>
+      </c>
+      <c r="F2256" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G2256" t="n">
+        <v>102700</v>
+      </c>
+      <c r="J2256" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2256" t="inlineStr">
+        <is>
+          <t>OI poll change +6.3% vs last scan (OI chg +102,700 | oi=1,739,790, was=1,637,090)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2257">
+      <c r="A2257" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:28:22</t>
+        </is>
+      </c>
+      <c r="B2257" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2257" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="K2257" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: -8,985,730 | New PE Vol: +616,850</t>
+        </is>
+      </c>
+    </row>
+    <row r="2258">
+      <c r="A2258" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:28:32</t>
+        </is>
+      </c>
+      <c r="B2258" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2258" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23300 CALL</t>
+        </is>
+      </c>
+      <c r="D2258" t="n">
+        <v>7198685</v>
+      </c>
+      <c r="E2258" t="n">
+        <v>6830200</v>
+      </c>
+      <c r="F2258" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G2258" t="n">
+        <v>368485</v>
+      </c>
+      <c r="J2258" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2258" t="inlineStr">
+        <is>
+          <t>OI poll change +5.4% vs last scan (OI chg +368,485 | oi=7,198,685, was=6,830,200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2259">
+      <c r="A2259" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:29:22</t>
+        </is>
+      </c>
+      <c r="B2259" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2259" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23250 CALL</t>
+        </is>
+      </c>
+      <c r="D2259" t="n">
+        <v>863525</v>
+      </c>
+      <c r="E2259" t="n">
+        <v>817570</v>
+      </c>
+      <c r="F2259" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G2259" t="n">
+        <v>45955</v>
+      </c>
+      <c r="J2259" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2259" t="inlineStr">
+        <is>
+          <t>OI poll change +5.6% vs last scan (OI chg +45,955 | oi=863,525, was=817,570)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2260">
+      <c r="A2260" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:29:23</t>
+        </is>
+      </c>
+      <c r="B2260" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2260" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="K2260" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: +12,060,750 | New PE Vol: +4,694,365</t>
+        </is>
+      </c>
+    </row>
+    <row r="2261">
+      <c r="A2261" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:30:23</t>
+        </is>
+      </c>
+      <c r="B2261" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2261" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23150 CALL</t>
+        </is>
+      </c>
+      <c r="D2261" t="n">
+        <v>224510</v>
+      </c>
+      <c r="E2261" t="n">
+        <v>202280</v>
+      </c>
+      <c r="F2261" t="n">
+        <v>11</v>
+      </c>
+      <c r="G2261" t="n">
+        <v>22230</v>
+      </c>
+      <c r="J2261" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2261" t="inlineStr">
+        <is>
+          <t>OI poll change +11.0% vs last scan (OI chg +22,230 | oi=224,510, was=202,280)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2262">
+      <c r="A2262" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:30:24</t>
+        </is>
+      </c>
+      <c r="B2262" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2262" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23250 PUT</t>
+        </is>
+      </c>
+      <c r="D2262" t="n">
+        <v>1912820</v>
+      </c>
+      <c r="E2262" t="n">
+        <v>1739790</v>
+      </c>
+      <c r="F2262" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="G2262" t="n">
+        <v>173030</v>
+      </c>
+      <c r="J2262" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2262" t="inlineStr">
+        <is>
+          <t>OI poll change +9.9% vs last scan (OI chg +173,030 | oi=1,912,820, was=1,739,790)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2263">
+      <c r="A2263" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:30:26</t>
+        </is>
+      </c>
+      <c r="B2263" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2263" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="K2263" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: -11,187,410 | New PE Vol: -669,110</t>
+        </is>
+      </c>
+    </row>
+    <row r="2264">
+      <c r="A2264" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:31:04</t>
+        </is>
+      </c>
+      <c r="B2264" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2264" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23300 CALL</t>
+        </is>
+      </c>
+      <c r="D2264" t="n">
+        <v>7665515</v>
+      </c>
+      <c r="E2264" t="n">
+        <v>3143205</v>
+      </c>
+      <c r="F2264" t="n">
+        <v>143.9</v>
+      </c>
+      <c r="G2264" t="n">
+        <v>4522310</v>
+      </c>
+      <c r="H2264" t="n">
+        <v>13110630</v>
+      </c>
+      <c r="K2264" t="inlineStr">
+        <is>
+          <t>periodic record vol=13,110,630 oi=7,665,515 (OI chg +4,522,310 +143.9%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2265">
+      <c r="A2265" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:31:05</t>
+        </is>
+      </c>
+      <c r="B2265" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2265" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23250 CALL</t>
+        </is>
+      </c>
+      <c r="D2265" t="n">
+        <v>914550</v>
+      </c>
+      <c r="E2265" t="n">
+        <v>126360</v>
+      </c>
+      <c r="F2265" t="n">
+        <v>623.8</v>
+      </c>
+      <c r="G2265" t="n">
+        <v>788190</v>
+      </c>
+      <c r="H2265" t="n">
+        <v>2381535</v>
+      </c>
+      <c r="K2265" t="inlineStr">
+        <is>
+          <t>periodic record vol=2,381,535 oi=914,550 (OI chg +788,190 +623.8%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2266">
+      <c r="A2266" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:31:06</t>
+        </is>
+      </c>
+      <c r="B2266" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2266" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23200 CALL</t>
+        </is>
+      </c>
+      <c r="D2266" t="n">
+        <v>1287000</v>
+      </c>
+      <c r="E2266" t="n">
+        <v>464880</v>
+      </c>
+      <c r="F2266" t="n">
+        <v>176.8</v>
+      </c>
+      <c r="G2266" t="n">
+        <v>822120</v>
+      </c>
+      <c r="H2266" t="n">
+        <v>2563340</v>
+      </c>
+      <c r="K2266" t="inlineStr">
+        <is>
+          <t>periodic record vol=2,563,340 oi=1,287,000 (OI chg +822,120 +176.8%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2267">
+      <c r="A2267" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:31:08</t>
+        </is>
+      </c>
+      <c r="B2267" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2267" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23300 PUT</t>
+        </is>
+      </c>
+      <c r="D2267" t="n">
+        <v>6768125</v>
+      </c>
+      <c r="E2267" t="n">
+        <v>5011045</v>
+      </c>
+      <c r="F2267" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="G2267" t="n">
+        <v>1757080</v>
+      </c>
+      <c r="H2267" t="n">
+        <v>24957205</v>
+      </c>
+      <c r="K2267" t="inlineStr">
+        <is>
+          <t>periodic record vol=24,957,205 oi=6,768,125 (OI chg +1,757,080 +35.1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2268">
+      <c r="A2268" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:31:09</t>
+        </is>
+      </c>
+      <c r="B2268" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2268" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23350 PUT</t>
+        </is>
+      </c>
+      <c r="D2268" t="n">
+        <v>1637220</v>
+      </c>
+      <c r="E2268" t="n">
+        <v>816270</v>
+      </c>
+      <c r="F2268" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="G2268" t="n">
+        <v>820950</v>
+      </c>
+      <c r="H2268" t="n">
+        <v>9467510</v>
+      </c>
+      <c r="K2268" t="inlineStr">
+        <is>
+          <t>periodic record vol=9,467,510 oi=1,637,220 (OI chg +820,950 +100.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2269">
+      <c r="A2269" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:31:10</t>
+        </is>
+      </c>
+      <c r="B2269" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2269" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23400 PUT</t>
+        </is>
+      </c>
+      <c r="D2269" t="n">
+        <v>3883815</v>
+      </c>
+      <c r="E2269" t="n">
+        <v>2959840</v>
+      </c>
+      <c r="F2269" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="G2269" t="n">
+        <v>923975</v>
+      </c>
+      <c r="H2269" t="n">
+        <v>12763205</v>
+      </c>
+      <c r="K2269" t="inlineStr">
+        <is>
+          <t>periodic record vol=12,763,205 oi=3,883,815 (OI chg +923,975 +31.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2270">
+      <c r="A2270" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:31:21</t>
+        </is>
+      </c>
+      <c r="B2270" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2270" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23250 CALL</t>
+        </is>
+      </c>
+      <c r="D2270" t="n">
+        <v>965575</v>
+      </c>
+      <c r="E2270" t="n">
+        <v>914550</v>
+      </c>
+      <c r="F2270" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G2270" t="n">
+        <v>51025</v>
+      </c>
+      <c r="J2270" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2270" t="inlineStr">
+        <is>
+          <t>OI poll change +5.6% vs last scan (OI chg +51,025 | oi=965,575, was=914,550)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2271">
+      <c r="A2271" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:31:31</t>
+        </is>
+      </c>
+      <c r="B2271" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2271" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="K2271" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: +13,550,355 | New PE Vol: +4,774,315</t>
+        </is>
+      </c>
+    </row>
+    <row r="2272">
+      <c r="A2272" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:32:35</t>
+        </is>
+      </c>
+      <c r="B2272" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2272" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="K2272" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: +1,550,965 | New PE Vol: +1,921,595</t>
+        </is>
+      </c>
+    </row>
+    <row r="2273">
+      <c r="A2273" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:32:55</t>
+        </is>
+      </c>
+      <c r="B2273" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2273" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23250 PUT</t>
+        </is>
+      </c>
+      <c r="D2273" t="n">
+        <v>2042560</v>
+      </c>
+      <c r="E2273" t="n">
+        <v>1912820</v>
+      </c>
+      <c r="F2273" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G2273" t="n">
+        <v>129740</v>
+      </c>
+      <c r="J2273" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2273" t="inlineStr">
+        <is>
+          <t>OI poll change +6.8% vs last scan (OI chg +129,740 | oi=2,042,560, was=1,912,820)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2274">
+      <c r="A2274" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:33:24</t>
+        </is>
+      </c>
+      <c r="B2274" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2274" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23250 CALL</t>
+        </is>
+      </c>
+      <c r="D2274" t="n">
+        <v>1063335</v>
+      </c>
+      <c r="E2274" t="n">
+        <v>1007825</v>
+      </c>
+      <c r="F2274" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G2274" t="n">
+        <v>55510</v>
+      </c>
+      <c r="J2274" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2274" t="inlineStr">
+        <is>
+          <t>OI poll change +5.5% vs last scan (OI chg +55,510 | oi=1,063,335, was=1,007,825)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2275">
+      <c r="A2275" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:33:44</t>
+        </is>
+      </c>
+      <c r="B2275" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2275" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="K2275" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: -13,464,750 | New PE Vol: +1,227,980</t>
+        </is>
+      </c>
+    </row>
+    <row r="2276">
+      <c r="A2276" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:34:53</t>
+        </is>
+      </c>
+      <c r="B2276" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2276" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="K2276" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: +384,020 | New PE Vol: +2,351,375</t>
+        </is>
+      </c>
+    </row>
+    <row r="2277">
+      <c r="A2277" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:35:24</t>
+        </is>
+      </c>
+      <c r="B2277" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2277" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23250 CALL</t>
+        </is>
+      </c>
+      <c r="D2277" t="n">
+        <v>1284530</v>
+      </c>
+      <c r="E2277" t="n">
+        <v>1152515</v>
+      </c>
+      <c r="F2277" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G2277" t="n">
+        <v>132015</v>
+      </c>
+      <c r="J2277" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2277" t="inlineStr">
+        <is>
+          <t>OI poll change +11.5% vs last scan (OI chg +132,015 | oi=1,284,530, was=1,152,515)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2278">
+      <c r="A2278" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:35:26</t>
+        </is>
+      </c>
+      <c r="B2278" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2278" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23200 CALL</t>
+        </is>
+      </c>
+      <c r="D2278" t="n">
+        <v>1516320</v>
+      </c>
+      <c r="E2278" t="n">
+        <v>1437150</v>
+      </c>
+      <c r="F2278" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G2278" t="n">
+        <v>79170</v>
+      </c>
+      <c r="J2278" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2278" t="inlineStr">
+        <is>
+          <t>OI poll change +5.5% vs last scan (OI chg +79,170 | oi=1,516,320, was=1,437,150)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2279">
+      <c r="A2279" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:36:01</t>
+        </is>
+      </c>
+      <c r="B2279" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2279" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="K2279" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: +1,031,875 | New PE Vol: +4,318,470</t>
+        </is>
+      </c>
+    </row>
+    <row r="2280">
+      <c r="A2280" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:36:12</t>
+        </is>
+      </c>
+      <c r="B2280" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2280" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23250 CALL</t>
+        </is>
+      </c>
+      <c r="D2280" t="n">
+        <v>1284530</v>
+      </c>
+      <c r="E2280" t="n">
+        <v>126360</v>
+      </c>
+      <c r="F2280" t="n">
+        <v>916.6</v>
+      </c>
+      <c r="G2280" t="n">
+        <v>1158170</v>
+      </c>
+      <c r="H2280" t="n">
+        <v>3996135</v>
+      </c>
+      <c r="K2280" t="inlineStr">
+        <is>
+          <t>periodic record vol=3,996,135 oi=1,284,530 (OI chg +1,158,170 +916.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2281">
+      <c r="A2281" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:36:12</t>
+        </is>
+      </c>
+      <c r="B2281" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2281" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23200 CALL</t>
+        </is>
+      </c>
+      <c r="D2281" t="n">
+        <v>1516320</v>
+      </c>
+      <c r="E2281" t="n">
+        <v>464880</v>
+      </c>
+      <c r="F2281" t="n">
+        <v>226.2</v>
+      </c>
+      <c r="G2281" t="n">
+        <v>1051440</v>
+      </c>
+      <c r="H2281" t="n">
+        <v>3682640</v>
+      </c>
+      <c r="K2281" t="inlineStr">
+        <is>
+          <t>periodic record vol=3,682,640 oi=1,516,320 (OI chg +1,051,440 +226.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2282">
+      <c r="A2282" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:36:13</t>
+        </is>
+      </c>
+      <c r="B2282" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2282" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23150 CALL</t>
+        </is>
+      </c>
+      <c r="D2282" t="n">
+        <v>236665</v>
+      </c>
+      <c r="E2282" t="n">
+        <v>32305</v>
+      </c>
+      <c r="F2282" t="n">
+        <v>632.6</v>
+      </c>
+      <c r="G2282" t="n">
+        <v>204360</v>
+      </c>
+      <c r="H2282" t="n">
+        <v>631735</v>
+      </c>
+      <c r="K2282" t="inlineStr">
+        <is>
+          <t>periodic record vol=631,735 oi=236,665 (OI chg +204,360 +632.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:36:14</t>
+        </is>
+      </c>
+      <c r="B2283" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2283" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23250 PUT</t>
+        </is>
+      </c>
+      <c r="D2283" t="n">
+        <v>2178345</v>
+      </c>
+      <c r="E2283" t="n">
+        <v>924950</v>
+      </c>
+      <c r="F2283" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="G2283" t="n">
+        <v>1253395</v>
+      </c>
+      <c r="H2283" t="n">
+        <v>14911065</v>
+      </c>
+      <c r="K2283" t="inlineStr">
+        <is>
+          <t>periodic record vol=14,911,065 oi=2,178,345 (OI chg +1,253,395 +135.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2284">
+      <c r="A2284" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:36:15</t>
+        </is>
+      </c>
+      <c r="B2284" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2284" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23300 PUT</t>
+        </is>
+      </c>
+      <c r="D2284" t="n">
+        <v>7013890</v>
+      </c>
+      <c r="E2284" t="n">
+        <v>5011045</v>
+      </c>
+      <c r="F2284" t="n">
+        <v>40</v>
+      </c>
+      <c r="G2284" t="n">
+        <v>2002845</v>
+      </c>
+      <c r="H2284" t="n">
+        <v>31887115</v>
+      </c>
+      <c r="K2284" t="inlineStr">
+        <is>
+          <t>periodic record vol=31,887,115 oi=7,013,890 (OI chg +2,002,845 +40.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="A2285" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:36:16</t>
+        </is>
+      </c>
+      <c r="B2285" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2285" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23350 PUT</t>
+        </is>
+      </c>
+      <c r="D2285" t="n">
+        <v>1644370</v>
+      </c>
+      <c r="E2285" t="n">
+        <v>816270</v>
+      </c>
+      <c r="F2285" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="G2285" t="n">
+        <v>828100</v>
+      </c>
+      <c r="H2285" t="n">
+        <v>11254620</v>
+      </c>
+      <c r="K2285" t="inlineStr">
+        <is>
+          <t>periodic record vol=11,254,620 oi=1,644,370 (OI chg +828,100 +101.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2286">
+      <c r="A2286" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:36:30</t>
+        </is>
+      </c>
+      <c r="B2286" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2286" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23300 CALL</t>
+        </is>
+      </c>
+      <c r="D2286" t="n">
+        <v>8570250</v>
+      </c>
+      <c r="E2286" t="n">
+        <v>7822360</v>
+      </c>
+      <c r="F2286" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="G2286" t="n">
+        <v>747890</v>
+      </c>
+      <c r="J2286" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2286" t="inlineStr">
+        <is>
+          <t>OI poll change +9.6% vs last scan (OI chg +747,890 | oi=8,570,250, was=7,822,360)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2287">
+      <c r="A2287" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:36:31</t>
+        </is>
+      </c>
+      <c r="B2287" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2287" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23250 CALL</t>
+        </is>
+      </c>
+      <c r="D2287" t="n">
+        <v>1350505</v>
+      </c>
+      <c r="E2287" t="n">
+        <v>1284530</v>
+      </c>
+      <c r="F2287" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G2287" t="n">
+        <v>65975</v>
+      </c>
+      <c r="J2287" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2287" t="inlineStr">
+        <is>
+          <t>OI poll change +5.1% vs last scan (OI chg +65,975 | oi=1,350,505, was=1,284,530)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2288">
+      <c r="A2288" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:36:31</t>
+        </is>
+      </c>
+      <c r="B2288" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2288" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23200 CALL</t>
+        </is>
+      </c>
+      <c r="D2288" t="n">
+        <v>1605825</v>
+      </c>
+      <c r="E2288" t="n">
+        <v>1516320</v>
+      </c>
+      <c r="F2288" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G2288" t="n">
+        <v>89505</v>
+      </c>
+      <c r="J2288" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2288" t="inlineStr">
+        <is>
+          <t>OI poll change +5.9% vs last scan (OI chg +89,505 | oi=1,605,825, was=1,516,320)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="A2289" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:36:52</t>
+        </is>
+      </c>
+      <c r="B2289" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="C2289" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23150 CALL</t>
+        </is>
+      </c>
+      <c r="D2289" t="n">
+        <v>258050</v>
+      </c>
+      <c r="E2289" t="n">
+        <v>236665</v>
+      </c>
+      <c r="F2289" t="n">
+        <v>9</v>
+      </c>
+      <c r="G2289" t="n">
+        <v>21385</v>
+      </c>
+      <c r="J2289" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="K2289" t="inlineStr">
+        <is>
+          <t>OI poll change +9.0% vs last scan (OI chg +21,385 | oi=258,050, was=236,665)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2290">
+      <c r="A2290" t="inlineStr">
+        <is>
+          <t>2026-06-03 09:37:02</t>
+        </is>
+      </c>
+      <c r="B2290" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2290" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="K2290" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: +674,830 | New PE Vol: +1,693,315</t>
+        </is>
+      </c>
+    </row>
+    <row r="2291">
+      <c r="A2291" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:42:16</t>
+        </is>
+      </c>
+      <c r="B2291" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2291" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23250 CALL</t>
+        </is>
+      </c>
+      <c r="D2291" t="n">
+        <v>3407495</v>
+      </c>
+      <c r="E2291" t="n">
+        <v>126360</v>
+      </c>
+      <c r="F2291" t="n">
+        <v>2596.7</v>
+      </c>
+      <c r="G2291" t="n">
+        <v>3281135</v>
+      </c>
+      <c r="H2291" t="n">
+        <v>23018840</v>
+      </c>
+      <c r="K2291" t="inlineStr">
+        <is>
+          <t>periodic record vol=23,018,840 oi=3,407,495 (OI chg +3,281,135 +2596.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2292">
+      <c r="A2292" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:42:18</t>
+        </is>
+      </c>
+      <c r="B2292" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2292" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23200 CALL</t>
+        </is>
+      </c>
+      <c r="D2292" t="n">
+        <v>2966925</v>
+      </c>
+      <c r="E2292" t="n">
+        <v>464880</v>
+      </c>
+      <c r="F2292" t="n">
+        <v>538.2</v>
+      </c>
+      <c r="G2292" t="n">
+        <v>2502045</v>
+      </c>
+      <c r="H2292" t="n">
+        <v>17509635</v>
+      </c>
+      <c r="K2292" t="inlineStr">
+        <is>
+          <t>periodic record vol=17,509,635 oi=2,966,925 (OI chg +2,502,045 +538.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2293">
+      <c r="A2293" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:42:20</t>
+        </is>
+      </c>
+      <c r="B2293" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2293" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23150 CALL</t>
+        </is>
+      </c>
+      <c r="D2293" t="n">
+        <v>431730</v>
+      </c>
+      <c r="E2293" t="n">
+        <v>32305</v>
+      </c>
+      <c r="F2293" t="n">
+        <v>1236.4</v>
+      </c>
+      <c r="G2293" t="n">
+        <v>399425</v>
+      </c>
+      <c r="H2293" t="n">
+        <v>2492750</v>
+      </c>
+      <c r="K2293" t="inlineStr">
+        <is>
+          <t>periodic record vol=2,492,750 oi=431,730 (OI chg +399,425 +1236.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:42:21</t>
+        </is>
+      </c>
+      <c r="B2294" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2294" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23250 PUT</t>
+        </is>
+      </c>
+      <c r="D2294" t="n">
+        <v>3442920</v>
+      </c>
+      <c r="E2294" t="n">
+        <v>924950</v>
+      </c>
+      <c r="F2294" t="n">
+        <v>272.2</v>
+      </c>
+      <c r="G2294" t="n">
+        <v>2517970</v>
+      </c>
+      <c r="H2294" t="n">
+        <v>50669450</v>
+      </c>
+      <c r="K2294" t="inlineStr">
+        <is>
+          <t>periodic record vol=50,669,450 oi=3,442,920 (OI chg +2,517,970 +272.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2295">
+      <c r="A2295" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:42:22</t>
+        </is>
+      </c>
+      <c r="B2295" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2295" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23300 PUT</t>
+        </is>
+      </c>
+      <c r="D2295" t="n">
+        <v>6889610</v>
+      </c>
+      <c r="E2295" t="n">
+        <v>5011045</v>
+      </c>
+      <c r="F2295" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="G2295" t="n">
+        <v>1878565</v>
+      </c>
+      <c r="H2295" t="n">
+        <v>77780040</v>
+      </c>
+      <c r="K2295" t="inlineStr">
+        <is>
+          <t>periodic record vol=77,780,040 oi=6,889,610 (OI chg +1,878,565 +37.5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2296">
+      <c r="A2296" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:42:23</t>
+        </is>
+      </c>
+      <c r="B2296" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2296" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23350 PUT</t>
+        </is>
+      </c>
+      <c r="D2296" t="n">
+        <v>1550705</v>
+      </c>
+      <c r="E2296" t="n">
+        <v>816270</v>
+      </c>
+      <c r="F2296" t="n">
+        <v>90</v>
+      </c>
+      <c r="G2296" t="n">
+        <v>734435</v>
+      </c>
+      <c r="H2296" t="n">
+        <v>20315295</v>
+      </c>
+      <c r="K2296" t="inlineStr">
+        <is>
+          <t>periodic record vol=20,315,295 oi=1,550,705 (OI chg +734,435 +90.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2297">
+      <c r="A2297" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:43:25</t>
+        </is>
+      </c>
+      <c r="B2297" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2297" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="K2297" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: +394,875 | New PE Vol: +656,045</t>
+        </is>
+      </c>
+    </row>
+    <row r="2298">
+      <c r="A2298" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:44:28</t>
+        </is>
+      </c>
+      <c r="B2298" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2298" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="K2298" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: +473,460 | New PE Vol: +728,390</t>
+        </is>
+      </c>
+    </row>
+    <row r="2299">
+      <c r="A2299" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:45:33</t>
+        </is>
+      </c>
+      <c r="B2299" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2299" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="K2299" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: +723,450 | New PE Vol: +1,898,065</t>
+        </is>
+      </c>
+    </row>
+    <row r="2300">
+      <c r="A2300" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:46:36</t>
+        </is>
+      </c>
+      <c r="B2300" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2300" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="K2300" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: +540,280 | New PE Vol: +674,505</t>
+        </is>
+      </c>
+    </row>
+    <row r="2301">
+      <c r="A2301" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:47:22</t>
+        </is>
+      </c>
+      <c r="B2301" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2301" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23250 CALL</t>
+        </is>
+      </c>
+      <c r="D2301" t="n">
+        <v>3475940</v>
+      </c>
+      <c r="E2301" t="n">
+        <v>126360</v>
+      </c>
+      <c r="F2301" t="n">
+        <v>2650.8</v>
+      </c>
+      <c r="G2301" t="n">
+        <v>3349580</v>
+      </c>
+      <c r="H2301" t="n">
+        <v>24286535</v>
+      </c>
+      <c r="K2301" t="inlineStr">
+        <is>
+          <t>periodic record vol=24,286,535 oi=3,475,940 (OI chg +3,349,580 +2650.8%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2302">
+      <c r="A2302" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:47:23</t>
+        </is>
+      </c>
+      <c r="B2302" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2302" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23200 CALL</t>
+        </is>
+      </c>
+      <c r="D2302" t="n">
+        <v>3015285</v>
+      </c>
+      <c r="E2302" t="n">
+        <v>464880</v>
+      </c>
+      <c r="F2302" t="n">
+        <v>548.6</v>
+      </c>
+      <c r="G2302" t="n">
+        <v>2550405</v>
+      </c>
+      <c r="H2302" t="n">
+        <v>18468645</v>
+      </c>
+      <c r="K2302" t="inlineStr">
+        <is>
+          <t>periodic record vol=18,468,645 oi=3,015,285 (OI chg +2,550,405 +548.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2303">
+      <c r="A2303" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:47:25</t>
+        </is>
+      </c>
+      <c r="B2303" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2303" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23150 CALL</t>
+        </is>
+      </c>
+      <c r="D2303" t="n">
+        <v>440310</v>
+      </c>
+      <c r="E2303" t="n">
+        <v>32305</v>
+      </c>
+      <c r="F2303" t="n">
+        <v>1263</v>
+      </c>
+      <c r="G2303" t="n">
+        <v>408005</v>
+      </c>
+      <c r="H2303" t="n">
+        <v>2626000</v>
+      </c>
+      <c r="K2303" t="inlineStr">
+        <is>
+          <t>periodic record vol=2,626,000 oi=440,310 (OI chg +408,005 +1263.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2304">
+      <c r="A2304" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:47:26</t>
+        </is>
+      </c>
+      <c r="B2304" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2304" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23250 PUT</t>
+        </is>
+      </c>
+      <c r="D2304" t="n">
+        <v>3495765</v>
+      </c>
+      <c r="E2304" t="n">
+        <v>924950</v>
+      </c>
+      <c r="F2304" t="n">
+        <v>277.9</v>
+      </c>
+      <c r="G2304" t="n">
+        <v>2570815</v>
+      </c>
+      <c r="H2304" t="n">
+        <v>52757055</v>
+      </c>
+      <c r="K2304" t="inlineStr">
+        <is>
+          <t>periodic record vol=52,757,055 oi=3,495,765 (OI chg +2,570,815 +277.9%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2305">
+      <c r="A2305" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:47:27</t>
+        </is>
+      </c>
+      <c r="B2305" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2305" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23300 PUT</t>
+        </is>
+      </c>
+      <c r="D2305" t="n">
+        <v>6963255</v>
+      </c>
+      <c r="E2305" t="n">
+        <v>5011045</v>
+      </c>
+      <c r="F2305" t="n">
+        <v>39</v>
+      </c>
+      <c r="G2305" t="n">
+        <v>1952210</v>
+      </c>
+      <c r="H2305" t="n">
+        <v>79805570</v>
+      </c>
+      <c r="K2305" t="inlineStr">
+        <is>
+          <t>periodic record vol=79,805,570 oi=6,963,255 (OI chg +1,952,210 +39.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2306">
+      <c r="A2306" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:47:29</t>
+        </is>
+      </c>
+      <c r="B2306" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2306" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23350 PUT</t>
+        </is>
+      </c>
+      <c r="D2306" t="n">
+        <v>1572090</v>
+      </c>
+      <c r="E2306" t="n">
+        <v>816270</v>
+      </c>
+      <c r="F2306" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="G2306" t="n">
+        <v>755820</v>
+      </c>
+      <c r="H2306" t="n">
+        <v>20658885</v>
+      </c>
+      <c r="K2306" t="inlineStr">
+        <is>
+          <t>periodic record vol=20,658,885 oi=1,572,090 (OI chg +755,820 +92.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="A2307" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:47:40</t>
+        </is>
+      </c>
+      <c r="B2307" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2307" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="K2307" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: +286,325 | New PE Vol: +637,390</t>
+        </is>
+      </c>
+    </row>
+    <row r="2308">
+      <c r="A2308" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:48:43</t>
+        </is>
+      </c>
+      <c r="B2308" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2308" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="K2308" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: +410,670 | New PE Vol: +593,840</t>
+        </is>
+      </c>
+    </row>
+    <row r="2309">
+      <c r="A2309" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:49:46</t>
+        </is>
+      </c>
+      <c r="B2309" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2309" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="K2309" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: +231,400 | New PE Vol: +424,450</t>
+        </is>
+      </c>
+    </row>
+    <row r="2310">
+      <c r="A2310" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:50:50</t>
+        </is>
+      </c>
+      <c r="B2310" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2310" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="K2310" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: +366,405 | New PE Vol: +444,080</t>
+        </is>
+      </c>
+    </row>
+    <row r="2311">
+      <c r="A2311" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:51:53</t>
+        </is>
+      </c>
+      <c r="B2311" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2311" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="K2311" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: +261,365 | New PE Vol: +378,495</t>
+        </is>
+      </c>
+    </row>
+    <row r="2312">
+      <c r="A2312" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:52:30</t>
+        </is>
+      </c>
+      <c r="B2312" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2312" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23250 CALL</t>
+        </is>
+      </c>
+      <c r="D2312" t="n">
+        <v>3523910</v>
+      </c>
+      <c r="E2312" t="n">
+        <v>126360</v>
+      </c>
+      <c r="F2312" t="n">
+        <v>2688.8</v>
+      </c>
+      <c r="G2312" t="n">
+        <v>3397550</v>
+      </c>
+      <c r="H2312" t="n">
+        <v>25047685</v>
+      </c>
+      <c r="K2312" t="inlineStr">
+        <is>
+          <t>periodic record vol=25,047,685 oi=3,523,910 (OI chg +3,397,550 +2688.8%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2313">
+      <c r="A2313" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:52:31</t>
+        </is>
+      </c>
+      <c r="B2313" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2313" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23200 CALL</t>
+        </is>
+      </c>
+      <c r="D2313" t="n">
+        <v>3119610</v>
+      </c>
+      <c r="E2313" t="n">
+        <v>464880</v>
+      </c>
+      <c r="F2313" t="n">
+        <v>571.1</v>
+      </c>
+      <c r="G2313" t="n">
+        <v>2654730</v>
+      </c>
+      <c r="H2313" t="n">
+        <v>19085690</v>
+      </c>
+      <c r="K2313" t="inlineStr">
+        <is>
+          <t>periodic record vol=19,085,690 oi=3,119,610 (OI chg +2,654,730 +571.1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2314">
+      <c r="A2314" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:52:33</t>
+        </is>
+      </c>
+      <c r="B2314" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2314" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23150 CALL</t>
+        </is>
+      </c>
+      <c r="D2314" t="n">
+        <v>443625</v>
+      </c>
+      <c r="E2314" t="n">
+        <v>32305</v>
+      </c>
+      <c r="F2314" t="n">
+        <v>1273.2</v>
+      </c>
+      <c r="G2314" t="n">
+        <v>411320</v>
+      </c>
+      <c r="H2314" t="n">
+        <v>2685605</v>
+      </c>
+      <c r="K2314" t="inlineStr">
+        <is>
+          <t>periodic record vol=2,685,605 oi=443,625 (OI chg +411,320 +1273.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2315">
+      <c r="A2315" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:52:34</t>
+        </is>
+      </c>
+      <c r="B2315" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2315" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23250 PUT</t>
+        </is>
+      </c>
+      <c r="D2315" t="n">
+        <v>3542500</v>
+      </c>
+      <c r="E2315" t="n">
+        <v>924950</v>
+      </c>
+      <c r="F2315" t="n">
+        <v>283</v>
+      </c>
+      <c r="G2315" t="n">
+        <v>2617550</v>
+      </c>
+      <c r="H2315" t="n">
+        <v>53744015</v>
+      </c>
+      <c r="K2315" t="inlineStr">
+        <is>
+          <t>periodic record vol=53,744,015 oi=3,542,500 (OI chg +2,617,550 +283.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2316">
+      <c r="A2316" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:52:36</t>
+        </is>
+      </c>
+      <c r="B2316" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2316" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23300 PUT</t>
+        </is>
+      </c>
+      <c r="D2316" t="n">
+        <v>6957730</v>
+      </c>
+      <c r="E2316" t="n">
+        <v>5011045</v>
+      </c>
+      <c r="F2316" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="G2316" t="n">
+        <v>1946685</v>
+      </c>
+      <c r="H2316" t="n">
+        <v>80777710</v>
+      </c>
+      <c r="K2316" t="inlineStr">
+        <is>
+          <t>periodic record vol=80,777,710 oi=6,957,730 (OI chg +1,946,685 +38.8%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2317">
+      <c r="A2317" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:52:37</t>
+        </is>
+      </c>
+      <c r="B2317" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2317" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23350 PUT</t>
+        </is>
+      </c>
+      <c r="D2317" t="n">
+        <v>1591005</v>
+      </c>
+      <c r="E2317" t="n">
+        <v>816270</v>
+      </c>
+      <c r="F2317" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="G2317" t="n">
+        <v>774735</v>
+      </c>
+      <c r="H2317" t="n">
+        <v>20827235</v>
+      </c>
+      <c r="K2317" t="inlineStr">
+        <is>
+          <t>periodic record vol=20,827,235 oi=1,591,005 (OI chg +774,735 +94.9%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2318">
+      <c r="A2318" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:52:57</t>
+        </is>
+      </c>
+      <c r="B2318" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2318" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="K2318" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: +195,780 | New PE Vol: +245,310</t>
+        </is>
+      </c>
+    </row>
+    <row r="2319">
+      <c r="A2319" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:53:59</t>
+        </is>
+      </c>
+      <c r="B2319" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2319" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="K2319" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: +413,270 | New PE Vol: +863,460</t>
+        </is>
+      </c>
+    </row>
+    <row r="2320">
+      <c r="A2320" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:55:00</t>
+        </is>
+      </c>
+      <c r="B2320" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2320" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="K2320" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: +340,145 | New PE Vol: +657,475</t>
+        </is>
+      </c>
+    </row>
+    <row r="2321">
+      <c r="A2321" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:56:02</t>
+        </is>
+      </c>
+      <c r="B2321" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2321" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="K2321" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: +469,105 | New PE Vol: +664,560</t>
+        </is>
+      </c>
+    </row>
+    <row r="2322">
+      <c r="A2322" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:57:05</t>
+        </is>
+      </c>
+      <c r="B2322" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2322" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="K2322" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: +241,735 | New PE Vol: +359,255</t>
+        </is>
+      </c>
+    </row>
+    <row r="2323">
+      <c r="A2323" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:57:33</t>
+        </is>
+      </c>
+      <c r="B2323" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2323" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23250 CALL</t>
+        </is>
+      </c>
+      <c r="D2323" t="n">
+        <v>3568045</v>
+      </c>
+      <c r="E2323" t="n">
+        <v>126360</v>
+      </c>
+      <c r="F2323" t="n">
+        <v>2723.7</v>
+      </c>
+      <c r="G2323" t="n">
+        <v>3441685</v>
+      </c>
+      <c r="H2323" t="n">
+        <v>25925055</v>
+      </c>
+      <c r="K2323" t="inlineStr">
+        <is>
+          <t>periodic record vol=25,925,055 oi=3,568,045 (OI chg +3,441,685 +2723.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2324">
+      <c r="A2324" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:57:35</t>
+        </is>
+      </c>
+      <c r="B2324" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2324" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23200 CALL</t>
+        </is>
+      </c>
+      <c r="D2324" t="n">
+        <v>3171285</v>
+      </c>
+      <c r="E2324" t="n">
+        <v>464880</v>
+      </c>
+      <c r="F2324" t="n">
+        <v>582.2</v>
+      </c>
+      <c r="G2324" t="n">
+        <v>2706405</v>
+      </c>
+      <c r="H2324" t="n">
+        <v>19856720</v>
+      </c>
+      <c r="K2324" t="inlineStr">
+        <is>
+          <t>periodic record vol=19,856,720 oi=3,171,285 (OI chg +2,706,405 +582.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2325">
+      <c r="A2325" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:57:36</t>
+        </is>
+      </c>
+      <c r="B2325" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2325" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23150 CALL</t>
+        </is>
+      </c>
+      <c r="D2325" t="n">
+        <v>441415</v>
+      </c>
+      <c r="E2325" t="n">
+        <v>32305</v>
+      </c>
+      <c r="F2325" t="n">
+        <v>1266.4</v>
+      </c>
+      <c r="G2325" t="n">
+        <v>409110</v>
+      </c>
+      <c r="H2325" t="n">
+        <v>2780440</v>
+      </c>
+      <c r="K2325" t="inlineStr">
+        <is>
+          <t>periodic record vol=2,780,440 oi=441,415 (OI chg +409,110 +1266.4%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2326">
+      <c r="A2326" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:57:38</t>
+        </is>
+      </c>
+      <c r="B2326" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2326" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23250 PUT</t>
+        </is>
+      </c>
+      <c r="D2326" t="n">
+        <v>3646955</v>
+      </c>
+      <c r="E2326" t="n">
+        <v>924950</v>
+      </c>
+      <c r="F2326" t="n">
+        <v>294.3</v>
+      </c>
+      <c r="G2326" t="n">
+        <v>2722005</v>
+      </c>
+      <c r="H2326" t="n">
+        <v>55235245</v>
+      </c>
+      <c r="K2326" t="inlineStr">
+        <is>
+          <t>periodic record vol=55,235,245 oi=3,646,955 (OI chg +2,722,005 +294.3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2327">
+      <c r="A2327" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:57:39</t>
+        </is>
+      </c>
+      <c r="B2327" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2327" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23300 PUT</t>
+        </is>
+      </c>
+      <c r="D2327" t="n">
+        <v>6923345</v>
+      </c>
+      <c r="E2327" t="n">
+        <v>5011045</v>
+      </c>
+      <c r="F2327" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="G2327" t="n">
+        <v>1912300</v>
+      </c>
+      <c r="H2327" t="n">
+        <v>82096820</v>
+      </c>
+      <c r="K2327" t="inlineStr">
+        <is>
+          <t>periodic record vol=82,096,820 oi=6,923,345 (OI chg +1,912,300 +38.2%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2328">
+      <c r="A2328" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:57:41</t>
+        </is>
+      </c>
+      <c r="B2328" t="inlineStr">
+        <is>
+          <t>Vol</t>
+        </is>
+      </c>
+      <c r="C2328" t="inlineStr">
+        <is>
+          <t>NIFTY 09 JUN 23350 PUT</t>
+        </is>
+      </c>
+      <c r="D2328" t="n">
+        <v>1608685</v>
+      </c>
+      <c r="E2328" t="n">
+        <v>816270</v>
+      </c>
+      <c r="F2328" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="G2328" t="n">
+        <v>792415</v>
+      </c>
+      <c r="H2328" t="n">
+        <v>21089705</v>
+      </c>
+      <c r="K2328" t="inlineStr">
+        <is>
+          <t>periodic record vol=21,089,705 oi=1,608,685 (OI chg +792,415 +97.1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2329">
+      <c r="A2329" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:58:09</t>
+        </is>
+      </c>
+      <c r="B2329" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2329" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="K2329" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: -22,021,545 | New PE Vol: +38,295,335</t>
+        </is>
+      </c>
+    </row>
+    <row r="2330">
+      <c r="A2330" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:59:14</t>
+        </is>
+      </c>
+      <c r="B2330" t="inlineStr">
+        <is>
+          <t>CHAIN_MACRO</t>
+        </is>
+      </c>
+      <c r="C2330" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="D2330" t="inlineStr"/>
+      <c r="E2330" t="inlineStr"/>
+      <c r="F2330" t="inlineStr"/>
+      <c r="G2330" t="inlineStr"/>
+      <c r="H2330" t="inlineStr"/>
+      <c r="I2330" t="inlineStr"/>
+      <c r="J2330" t="inlineStr"/>
+      <c r="K2330" t="inlineStr">
+        <is>
+          <t>Chain Activity Check - New CE Vol: +23,207,080 | New PE Vol: -35,847,435</t>
         </is>
       </c>
     </row>
